--- a/data/2024-25/AHLdelegacije.xlsx
+++ b/data/2024-25/AHLdelegacije.xlsx
@@ -1,11 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29328"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A9C49DF-1202-4C32-B7F5-03989AAA0670}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C00483DE-3F50-4D06-8CAE-5421694A5519}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="AHL" sheetId="1" r:id="rId1"/>
@@ -31,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3281" uniqueCount="519">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3280" uniqueCount="518">
   <si>
     <t>sl</t>
   </si>
@@ -1237,9 +1237,6 @@
   </si>
   <si>
     <t>Eishalle Cortina;LazzeriAl;RivisFe;MoidlMa;RinkerDa</t>
-  </si>
-  <si>
-    <t>ZBRISANO</t>
   </si>
   <si>
     <t>Eishalle Dornbirn;RuetzMa;VirtaTu;FleischmannLu;IlmerNo</t>
@@ -2079,6 +2076,7 @@
     <xf numFmtId="9" fontId="0" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2097,7 +2095,6 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -11486,11 +11483,18 @@
     <col min="78" max="78" width="56.28515625" customWidth="1"/>
     <col min="79" max="79" width="41.28515625" customWidth="1"/>
     <col min="80" max="80" width="75.7109375" customWidth="1"/>
-    <col min="81" max="81" width="65.7109375" customWidth="1"/>
+    <col min="81" max="81" width="86" customWidth="1"/>
     <col min="82" max="82" width="52.28515625" customWidth="1"/>
     <col min="83" max="83" width="49.7109375" customWidth="1"/>
+    <col min="84" max="84" width="47.7109375" customWidth="1"/>
+    <col min="85" max="85" width="55.7109375" customWidth="1"/>
+    <col min="86" max="86" width="26.28515625" customWidth="1"/>
+    <col min="88" max="88" width="51.42578125" customWidth="1"/>
     <col min="89" max="89" width="44.42578125" customWidth="1"/>
     <col min="90" max="90" width="54.28515625" customWidth="1"/>
+    <col min="91" max="91" width="17" customWidth="1"/>
+    <col min="92" max="92" width="65.5703125" customWidth="1"/>
+    <col min="93" max="93" width="41.7109375" customWidth="1"/>
     <col min="101" max="101" width="66.85546875" customWidth="1"/>
     <col min="104" max="104" width="57.5703125" customWidth="1"/>
   </cols>
@@ -11805,7 +11809,7 @@
       <c r="CY3" t="s">
         <v>175</v>
       </c>
-      <c r="CZ3" s="67"/>
+      <c r="CZ3" s="61"/>
     </row>
     <row r="4" spans="1:104" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
@@ -12490,299 +12494,296 @@
       <c r="CL6" t="s">
         <v>401</v>
       </c>
-      <c r="CN6" t="s">
-        <v>402</v>
-      </c>
     </row>
     <row r="7" spans="1:104" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
+        <v>402</v>
+      </c>
+      <c r="D7" t="s">
         <v>403</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
         <v>404</v>
       </c>
-      <c r="F7" t="s">
+      <c r="G7" t="s">
         <v>405</v>
       </c>
-      <c r="G7" t="s">
+      <c r="H7" t="s">
         <v>406</v>
       </c>
-      <c r="H7" t="s">
+      <c r="K7" t="s">
         <v>407</v>
       </c>
-      <c r="K7" t="s">
+      <c r="L7" t="s">
         <v>408</v>
-      </c>
-      <c r="L7" t="s">
-        <v>409</v>
       </c>
       <c r="N7" t="s">
         <v>391</v>
       </c>
       <c r="P7" t="s">
+        <v>409</v>
+      </c>
+      <c r="T7" t="s">
         <v>410</v>
       </c>
-      <c r="T7" t="s">
+      <c r="V7" t="s">
         <v>411</v>
       </c>
-      <c r="V7" t="s">
+      <c r="W7" t="s">
         <v>412</v>
       </c>
-      <c r="W7" t="s">
+      <c r="Y7" t="s">
         <v>413</v>
       </c>
-      <c r="Y7" t="s">
+      <c r="Z7" t="s">
         <v>414</v>
       </c>
-      <c r="Z7" t="s">
+      <c r="AB7" t="s">
         <v>415</v>
       </c>
-      <c r="AB7" t="s">
+      <c r="AD7" t="s">
         <v>416</v>
       </c>
-      <c r="AD7" t="s">
+      <c r="AE7" t="s">
         <v>417</v>
       </c>
-      <c r="AE7" t="s">
+      <c r="AI7" t="s">
         <v>418</v>
       </c>
-      <c r="AI7" t="s">
+      <c r="AK7" t="s">
         <v>419</v>
       </c>
-      <c r="AK7" t="s">
+      <c r="AM7" t="s">
         <v>420</v>
       </c>
-      <c r="AM7" t="s">
+      <c r="AN7" t="s">
         <v>421</v>
       </c>
-      <c r="AN7" t="s">
+      <c r="AO7" t="s">
         <v>422</v>
       </c>
-      <c r="AO7" t="s">
+      <c r="AS7" t="s">
         <v>423</v>
       </c>
-      <c r="AS7" t="s">
+      <c r="AT7" t="s">
         <v>424</v>
       </c>
-      <c r="AT7" t="s">
+      <c r="AU7" t="s">
         <v>425</v>
       </c>
-      <c r="AU7" t="s">
+      <c r="AV7" t="s">
         <v>426</v>
       </c>
-      <c r="AV7" t="s">
+      <c r="AW7" t="s">
         <v>427</v>
       </c>
-      <c r="AW7" t="s">
+      <c r="AX7" t="s">
         <v>428</v>
       </c>
-      <c r="AX7" t="s">
+      <c r="AZ7" t="s">
         <v>429</v>
       </c>
-      <c r="AZ7" t="s">
+      <c r="BC7" t="s">
         <v>430</v>
       </c>
-      <c r="BC7" t="s">
+      <c r="BG7" t="s">
         <v>431</v>
       </c>
-      <c r="BG7" t="s">
+      <c r="BJ7" t="s">
         <v>432</v>
       </c>
-      <c r="BJ7" t="s">
+      <c r="BK7" t="s">
         <v>433</v>
       </c>
-      <c r="BK7" t="s">
+      <c r="BM7" t="s">
         <v>434</v>
       </c>
-      <c r="BM7" t="s">
+      <c r="BN7" t="s">
         <v>435</v>
       </c>
-      <c r="BN7" t="s">
+      <c r="BS7" t="s">
         <v>436</v>
       </c>
-      <c r="BS7" t="s">
+      <c r="BV7" t="s">
         <v>437</v>
       </c>
-      <c r="BV7" t="s">
+      <c r="BX7" t="s">
         <v>438</v>
       </c>
-      <c r="BX7" t="s">
+      <c r="BY7" t="s">
         <v>439</v>
       </c>
-      <c r="BY7" t="s">
+      <c r="BZ7" t="s">
         <v>440</v>
       </c>
-      <c r="BZ7" t="s">
+      <c r="CA7" t="s">
         <v>441</v>
       </c>
-      <c r="CA7" t="s">
+      <c r="CB7" t="s">
         <v>442</v>
       </c>
-      <c r="CB7" t="s">
+      <c r="CC7" t="s">
         <v>443</v>
       </c>
-      <c r="CC7" t="s">
+      <c r="CF7" t="s">
         <v>444</v>
       </c>
-      <c r="CF7" t="s">
+      <c r="CG7" t="s">
         <v>445</v>
       </c>
-      <c r="CG7" t="s">
+      <c r="CH7" t="s">
         <v>446</v>
       </c>
-      <c r="CH7" t="s">
+      <c r="CI7" t="s">
         <v>447</v>
       </c>
-      <c r="CI7" t="s">
+      <c r="CJ7" t="s">
         <v>448</v>
       </c>
-      <c r="CJ7" t="s">
+      <c r="CK7" t="s">
         <v>449</v>
-      </c>
-      <c r="CK7" t="s">
-        <v>450</v>
       </c>
     </row>
     <row r="8" spans="1:104" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
+        <v>450</v>
+      </c>
+      <c r="D8" t="s">
         <v>451</v>
       </c>
-      <c r="D8" t="s">
+      <c r="F8" t="s">
         <v>452</v>
       </c>
-      <c r="F8" t="s">
+      <c r="G8" t="s">
         <v>453</v>
       </c>
-      <c r="G8" t="s">
+      <c r="H8" t="s">
         <v>454</v>
       </c>
-      <c r="H8" t="s">
+      <c r="K8" t="s">
         <v>455</v>
       </c>
-      <c r="K8" t="s">
+      <c r="L8" t="s">
         <v>456</v>
       </c>
-      <c r="L8" t="s">
+      <c r="V8" t="s">
         <v>457</v>
       </c>
-      <c r="V8" t="s">
+      <c r="W8" t="s">
         <v>458</v>
       </c>
-      <c r="W8" t="s">
+      <c r="Y8" t="s">
         <v>459</v>
       </c>
-      <c r="Y8" t="s">
+      <c r="AB8" t="s">
         <v>460</v>
       </c>
-      <c r="AB8" t="s">
+      <c r="AD8" t="s">
         <v>461</v>
       </c>
-      <c r="AD8" t="s">
+      <c r="AE8" t="s">
         <v>462</v>
       </c>
-      <c r="AE8" t="s">
+      <c r="AI8" t="s">
         <v>463</v>
       </c>
-      <c r="AI8" t="s">
+      <c r="AK8" t="s">
         <v>464</v>
       </c>
-      <c r="AK8" t="s">
+      <c r="AM8" t="s">
         <v>465</v>
       </c>
-      <c r="AM8" t="s">
+      <c r="AO8" t="s">
         <v>466</v>
       </c>
-      <c r="AO8" t="s">
+      <c r="AT8" t="s">
         <v>467</v>
       </c>
-      <c r="AT8" t="s">
+      <c r="AU8" t="s">
         <v>468</v>
       </c>
-      <c r="AU8" t="s">
+      <c r="AW8" t="s">
         <v>469</v>
       </c>
-      <c r="AW8" t="s">
+      <c r="AZ8" t="s">
         <v>470</v>
       </c>
-      <c r="AZ8" t="s">
+      <c r="BC8" t="s">
         <v>471</v>
       </c>
-      <c r="BC8" t="s">
+      <c r="BK8" t="s">
         <v>472</v>
       </c>
-      <c r="BK8" t="s">
+      <c r="BM8" t="s">
         <v>473</v>
       </c>
-      <c r="BM8" t="s">
+      <c r="BS8" t="s">
         <v>474</v>
       </c>
-      <c r="BS8" t="s">
+      <c r="BX8" t="s">
         <v>475</v>
       </c>
-      <c r="BX8" t="s">
+      <c r="BY8" t="s">
         <v>476</v>
       </c>
-      <c r="BY8" t="s">
+      <c r="BZ8" t="s">
         <v>477</v>
       </c>
-      <c r="BZ8" t="s">
+      <c r="CA8" t="s">
         <v>478</v>
       </c>
-      <c r="CA8" t="s">
+      <c r="CB8" t="s">
         <v>479</v>
       </c>
-      <c r="CB8" t="s">
+      <c r="CC8" t="s">
         <v>480</v>
       </c>
-      <c r="CC8" t="s">
+      <c r="CF8" t="s">
         <v>481</v>
       </c>
-      <c r="CF8" t="s">
+      <c r="CG8" t="s">
         <v>482</v>
-      </c>
-      <c r="CG8" t="s">
-        <v>483</v>
       </c>
     </row>
     <row r="9" spans="1:104" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="G9" t="s">
+        <v>483</v>
+      </c>
+      <c r="L9" t="s">
         <v>484</v>
       </c>
-      <c r="L9" t="s">
+      <c r="AD9" t="s">
         <v>485</v>
       </c>
-      <c r="AD9" t="s">
+      <c r="AE9" t="s">
         <v>486</v>
       </c>
-      <c r="AE9" t="s">
+      <c r="AK9" t="s">
         <v>487</v>
       </c>
-      <c r="AK9" t="s">
+      <c r="AT9" t="s">
         <v>488</v>
       </c>
-      <c r="AT9" t="s">
+      <c r="BC9" t="s">
         <v>489</v>
       </c>
-      <c r="BC9" t="s">
+      <c r="BK9" t="s">
         <v>490</v>
       </c>
-      <c r="BK9" t="s">
+      <c r="BX9" t="s">
         <v>491</v>
       </c>
-      <c r="BX9" t="s">
+      <c r="BZ9" t="s">
         <v>492</v>
       </c>
-      <c r="BZ9" t="s">
+      <c r="CA9" t="s">
         <v>493</v>
       </c>
-      <c r="CA9" t="s">
+      <c r="CB9" t="s">
         <v>494</v>
       </c>
-      <c r="CB9" t="s">
+      <c r="CC9" t="s">
         <v>495</v>
-      </c>
-      <c r="CC9" t="s">
-        <v>496</v>
       </c>
     </row>
     <row r="10" spans="1:104" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -12818,43 +12819,43 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="61" t="s">
-        <v>497</v>
-      </c>
-      <c r="B1" s="62"/>
+      <c r="A1" s="62" t="s">
+        <v>496</v>
+      </c>
+      <c r="B1" s="63"/>
       <c r="C1" s="6">
         <f>COUNTIF(AHL_DAT_STRING!4:18,"&lt;&gt;")</f>
-        <v>322</v>
+        <v>321</v>
       </c>
     </row>
     <row r="2" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="63" t="s">
-        <v>498</v>
-      </c>
-      <c r="B2" s="64"/>
+      <c r="A2" s="64" t="s">
+        <v>497</v>
+      </c>
+      <c r="B2" s="65"/>
       <c r="C2" s="7">
         <f>C1*4</f>
-        <v>1288</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="8" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B3" s="9">
         <f>COUNTIF(AHL!4:50, "&lt;&gt;")</f>
         <v>1284</v>
       </c>
-      <c r="E3" s="65" t="s">
-        <v>499</v>
-      </c>
-      <c r="F3" s="64"/>
-      <c r="G3" s="64"/>
-      <c r="H3" s="64"/>
+      <c r="E3" s="66" t="s">
+        <v>498</v>
+      </c>
+      <c r="F3" s="65"/>
+      <c r="G3" s="65"/>
+      <c r="H3" s="65"/>
     </row>
     <row r="4" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B4" s="11">
         <f>SUMIF(AHL!2:2,"sl",AHL!1:1)</f>
@@ -12865,28 +12866,28 @@
         <v>29</v>
       </c>
       <c r="E4" t="s">
+        <v>500</v>
+      </c>
+      <c r="F4" t="s">
         <v>501</v>
       </c>
-      <c r="F4" t="s">
+      <c r="G4" t="s">
         <v>502</v>
       </c>
-      <c r="G4" t="s">
+      <c r="H4" t="s">
         <v>503</v>
       </c>
-      <c r="H4" t="s">
+      <c r="I4" t="s">
         <v>504</v>
       </c>
-      <c r="I4" t="s">
+      <c r="J4" t="s">
         <v>505</v>
       </c>
-      <c r="J4" t="s">
+      <c r="K4" t="s">
         <v>506</v>
       </c>
-      <c r="K4" t="s">
+      <c r="L4" t="s">
         <v>507</v>
-      </c>
-      <c r="L4" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="5" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12898,7 +12899,7 @@
         <v>33</v>
       </c>
       <c r="E5" s="12" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F5" s="13">
         <v>2</v>
@@ -12913,7 +12914,7 @@
       </c>
       <c r="I5" s="16">
         <f>C2*G5</f>
-        <v>198.15384615384616</v>
+        <v>197.53846153846155</v>
       </c>
       <c r="J5">
         <f>B4</f>
@@ -12921,11 +12922,11 @@
       </c>
       <c r="K5" s="17">
         <f>J5-I5</f>
-        <v>-4.1538461538461604</v>
+        <v>-3.5384615384615472</v>
       </c>
       <c r="L5" s="18">
         <f>K5/4</f>
-        <v>-1.0384615384615401</v>
+        <v>-0.8846153846153868</v>
       </c>
     </row>
     <row r="6" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12956,7 +12957,7 @@
       </c>
       <c r="I6" s="16">
         <f>C2*G6</f>
-        <v>99.07692307692308</v>
+        <v>98.769230769230774</v>
       </c>
       <c r="J6">
         <f>B5</f>
@@ -12964,11 +12965,11 @@
       </c>
       <c r="K6" s="17">
         <f>J6-I6</f>
-        <v>-66.07692307692308</v>
+        <v>-65.769230769230774</v>
       </c>
       <c r="L6" s="18">
         <f t="shared" ref="L6" si="0">K6/4</f>
-        <v>-16.51923076923077</v>
+        <v>-16.442307692307693</v>
       </c>
     </row>
     <row r="7" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12984,7 +12985,7 @@
         <v>163</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F7" s="22">
         <v>3</v>
@@ -12999,7 +13000,7 @@
       </c>
       <c r="I7" s="16">
         <f>C2*G7</f>
-        <v>297.23076923076923</v>
+        <v>296.30769230769232</v>
       </c>
       <c r="J7">
         <f>B4+B5</f>
@@ -13007,23 +13008,23 @@
       </c>
       <c r="K7" s="17">
         <f>J7-I7</f>
-        <v>-70.230769230769226</v>
+        <v>-69.307692307692321</v>
       </c>
       <c r="L7" s="18">
         <f>K7/4</f>
-        <v>-17.557692307692307</v>
+        <v>-17.32692307692308</v>
       </c>
     </row>
     <row r="8" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="25" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="C8">
         <f>SUM(C4:C7)</f>
         <v>209</v>
       </c>
       <c r="E8" s="26" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F8" s="27">
         <v>6</v>
@@ -13038,7 +13039,7 @@
       </c>
       <c r="I8" s="16">
         <f>C2*G8</f>
-        <v>594.46153846153845</v>
+        <v>592.61538461538464</v>
       </c>
       <c r="J8">
         <f>B6</f>
@@ -13046,23 +13047,23 @@
       </c>
       <c r="K8" s="17">
         <f>J8-I8</f>
-        <v>-100.46153846153845</v>
+        <v>-98.615384615384642</v>
       </c>
       <c r="L8" s="18">
         <f>K8/4</f>
-        <v>-25.115384615384613</v>
+        <v>-24.65384615384616</v>
       </c>
     </row>
     <row r="9" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B9">
         <f>SUM(B4:B7)</f>
         <v>1284</v>
       </c>
       <c r="E9" s="26" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F9" s="27">
         <v>4</v>
@@ -13077,7 +13078,7 @@
       </c>
       <c r="I9" s="16">
         <f>C2*G9</f>
-        <v>396.30769230769232</v>
+        <v>395.07692307692309</v>
       </c>
       <c r="J9">
         <f>B7</f>
@@ -13085,20 +13086,20 @@
       </c>
       <c r="K9" s="30">
         <f>J9-I9</f>
-        <v>166.69230769230768</v>
+        <v>167.92307692307691</v>
       </c>
       <c r="L9" s="18">
         <f>K9/4</f>
-        <v>41.67307692307692</v>
+        <v>41.980769230769226</v>
       </c>
     </row>
     <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="H11" s="31" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="I11" s="32">
         <f>SUM(I7:I9)</f>
-        <v>1288</v>
+        <v>1284</v>
       </c>
       <c r="J11" s="26">
         <f>SUM(J7:J9)</f>
@@ -13106,42 +13107,42 @@
       </c>
       <c r="K11" s="33">
         <f>SUM(K7:K9)</f>
-        <v>-4</v>
+        <v>0</v>
       </c>
       <c r="L11" s="34">
         <f>SUM(L7:L9)</f>
-        <v>-1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:12" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E16" t="s">
+        <v>514</v>
+      </c>
+      <c r="F16" t="s">
+        <v>501</v>
+      </c>
+      <c r="G16" t="s">
         <v>515</v>
       </c>
-      <c r="F16" t="s">
-        <v>502</v>
-      </c>
-      <c r="G16" t="s">
-        <v>516</v>
-      </c>
       <c r="H16" t="s">
+        <v>503</v>
+      </c>
+      <c r="I16" s="35" t="s">
         <v>504</v>
       </c>
-      <c r="I16" s="35" t="s">
+      <c r="J16" s="35" t="s">
         <v>505</v>
       </c>
-      <c r="J16" s="35" t="s">
+      <c r="K16" t="s">
         <v>506</v>
       </c>
-      <c r="K16" t="s">
+      <c r="L16" t="s">
         <v>507</v>
-      </c>
-      <c r="L16" t="s">
-        <v>508</v>
       </c>
     </row>
     <row r="17" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E17" s="36" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F17" s="37">
         <v>3</v>
@@ -13173,7 +13174,7 @@
     </row>
     <row r="18" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E18" s="43" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F18" s="44">
         <v>6</v>
@@ -13206,7 +13207,7 @@
     </row>
     <row r="19" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E19" s="51" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F19" s="52">
         <v>4</v>
@@ -13237,39 +13238,39 @@
       </c>
     </row>
     <row r="21" spans="5:17" ht="46.5" customHeight="1" x14ac:dyDescent="0.7">
-      <c r="E21" s="66" t="s">
-        <v>517</v>
-      </c>
-      <c r="F21" s="66"/>
-      <c r="G21" s="66"/>
-      <c r="H21" s="66"/>
-      <c r="I21" s="66"/>
-      <c r="J21" s="66"/>
-      <c r="K21" s="66"/>
+      <c r="E21" s="67" t="s">
+        <v>516</v>
+      </c>
+      <c r="F21" s="67"/>
+      <c r="G21" s="67"/>
+      <c r="H21" s="67"/>
+      <c r="I21" s="67"/>
+      <c r="J21" s="67"/>
+      <c r="K21" s="67"/>
     </row>
     <row r="22" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F22" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G22" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="H22" t="s">
+        <v>503</v>
+      </c>
+      <c r="I22" s="35" t="s">
         <v>504</v>
       </c>
-      <c r="I22" s="35" t="s">
+      <c r="J22" s="35" t="s">
         <v>505</v>
       </c>
-      <c r="J22" s="35" t="s">
+      <c r="K22" t="s">
         <v>506</v>
-      </c>
-      <c r="K22" t="s">
-        <v>507</v>
       </c>
     </row>
     <row r="23" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E23" s="36" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F23" s="37">
         <v>3</v>
@@ -13297,7 +13298,7 @@
     </row>
     <row r="24" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E24" s="43" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F24" s="44">
         <v>6</v>
@@ -13325,7 +13326,7 @@
     </row>
     <row r="25" spans="5:17" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="E25" s="51" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F25" s="52">
         <v>4</v>
@@ -13353,7 +13354,7 @@
     </row>
     <row r="26" spans="5:17" x14ac:dyDescent="0.25">
       <c r="E26" s="5" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
@@ -13370,7 +13371,7 @@
     </row>
     <row r="28" spans="5:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="H28" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="J28">
         <f>SUM(J23:J26)</f>
